--- a/data/documents/xlsx/defect_pareto_log.xlsx
+++ b/data/documents/xlsx/defect_pareto_log.xlsx
@@ -1,14 +1,415 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
   <sheets>
-    <sheet name="defect_pareto_log" sheetId="1" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="defect_pareto_log" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
+  <definedNames/>
 </workbook>
+</file>
+
+<file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="1">
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+  </fonts>
+  <fills count="2">
+    <fill>
+      <patternFill/>
+    </fill>
+    <fill>
+      <patternFill patternType="gray125"/>
+    </fill>
+  </fills>
+  <borders count="1">
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+  </borders>
+  <cellStyleXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+  </cellStyleXfs>
+  <cellXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+  </cellXfs>
+  <cellStyles count="1">
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+  </cellStyles>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
+</styleSheet>
+</file>
+
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+  <a:themeElements>
+    <a:clrScheme name="Office">
+      <a:dk1>
+        <a:sysClr val="windowText" lastClr="000000"/>
+      </a:dk1>
+      <a:lt1>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
+      </a:lt1>
+      <a:dk2>
+        <a:srgbClr val="1F497D"/>
+      </a:dk2>
+      <a:lt2>
+        <a:srgbClr val="EEECE1"/>
+      </a:lt2>
+      <a:accent1>
+        <a:srgbClr val="4F81BD"/>
+      </a:accent1>
+      <a:accent2>
+        <a:srgbClr val="C0504D"/>
+      </a:accent2>
+      <a:accent3>
+        <a:srgbClr val="9BBB59"/>
+      </a:accent3>
+      <a:accent4>
+        <a:srgbClr val="8064A2"/>
+      </a:accent4>
+      <a:accent5>
+        <a:srgbClr val="4BACC6"/>
+      </a:accent5>
+      <a:accent6>
+        <a:srgbClr val="F79646"/>
+      </a:accent6>
+      <a:hlink>
+        <a:srgbClr val="0000FF"/>
+      </a:hlink>
+      <a:folHlink>
+        <a:srgbClr val="800080"/>
+      </a:folHlink>
+    </a:clrScheme>
+    <a:fontScheme name="Office">
+      <a:majorFont>
+        <a:latin typeface="Cambria"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+      </a:majorFont>
+      <a:minorFont>
+        <a:latin typeface="Calibri"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+      </a:minorFont>
+    </a:fontScheme>
+    <a:fmtScheme name="Office">
+      <a:fillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="50000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="35000">
+              <a:schemeClr val="phClr">
+                <a:tint val="37000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:tint val="15000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="16200000" scaled="1"/>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:shade val="51000"/>
+                <a:satMod val="130000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="80000">
+              <a:schemeClr val="phClr">
+                <a:shade val="93000"/>
+                <a:satMod val="130000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="94000"/>
+                <a:satMod val="135000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="16200000" scaled="0"/>
+        </a:gradFill>
+      </a:fillStyleLst>
+      <a:lnStyleLst>
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr">
+              <a:shade val="95000"/>
+              <a:satMod val="105000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </a:lnStyleLst>
+      <a:effectStyleLst>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="38000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot lat="0" lon="0" rev="0"/>
+            </a:camera>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d>
+            <a:bevelT w="63500" h="25400"/>
+          </a:sp3d>
+        </a:effectStyle>
+      </a:effectStyleLst>
+      <a:bgFillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="40000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="40000">
+              <a:schemeClr val="phClr">
+                <a:tint val="45000"/>
+                <a:shade val="99000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="20000"/>
+                <a:satMod val="255000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
+          </a:path>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="80000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="30000"/>
+                <a:satMod val="200000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+          </a:path>
+        </a:gradFill>
+      </a:bgFillStyleLst>
+    </a:fmtScheme>
+  </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
+</a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I23"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -65,7 +466,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2024-01-14</t>
+          <t>2026-01-11</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -83,7 +484,7 @@
           <t>Metal 3</t>
         </is>
       </c>
-      <c r="F2">
+      <c r="F2" t="n">
         <v>184</v>
       </c>
       <c r="G2" t="inlineStr">
@@ -110,7 +511,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2024-01-14</t>
+          <t>2026-01-11</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -128,7 +529,7 @@
           <t>Metal 1</t>
         </is>
       </c>
-      <c r="F3">
+      <c r="F3" t="n">
         <v>42</v>
       </c>
       <c r="G3" t="inlineStr">
@@ -155,7 +556,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2024-01-15</t>
+          <t>2026-01-12</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -173,7 +574,7 @@
           <t>ILD-3</t>
         </is>
       </c>
-      <c r="F4">
+      <c r="F4" t="n">
         <v>96</v>
       </c>
       <c r="G4" t="inlineStr">
@@ -200,7 +601,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2024-01-18</t>
+          <t>2026-01-15</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -218,7 +619,7 @@
           <t>Poly Gate</t>
         </is>
       </c>
-      <c r="F5">
+      <c r="F5" t="n">
         <v>14</v>
       </c>
       <c r="G5" t="inlineStr">
@@ -245,7 +646,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2024-01-22</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -263,7 +664,7 @@
           <t>Metal 3</t>
         </is>
       </c>
-      <c r="F6">
+      <c r="F6" t="n">
         <v>152</v>
       </c>
       <c r="G6" t="inlineStr">
@@ -290,7 +691,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2024-01-28</t>
+          <t>2026-01-25</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -308,7 +709,7 @@
           <t>Via 2</t>
         </is>
       </c>
-      <c r="F7">
+      <c r="F7" t="n">
         <v>28</v>
       </c>
       <c r="G7" t="inlineStr">
@@ -318,7 +719,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Polymer polymer accumulation in reactive ion etch chamber</t>
+          <t>Polymer accumulation in reactive ion etch chamber</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -335,7 +736,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2024-02-04</t>
+          <t>2026-02-01</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -353,7 +754,7 @@
           <t>Metal 3</t>
         </is>
       </c>
-      <c r="F8">
+      <c r="F8" t="n">
         <v>36</v>
       </c>
       <c r="G8" t="inlineStr">
@@ -380,7 +781,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2024-02-08</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -398,7 +799,7 @@
           <t>IO Ring</t>
         </is>
       </c>
-      <c r="F9">
+      <c r="F9" t="n">
         <v>68</v>
       </c>
       <c r="G9" t="inlineStr">
@@ -425,7 +826,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2024-02-15</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -443,7 +844,7 @@
           <t>Nitride</t>
         </is>
       </c>
-      <c r="F10">
+      <c r="F10" t="n">
         <v>11</v>
       </c>
       <c r="G10" t="inlineStr">
@@ -470,7 +871,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2024-02-22</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -488,7 +889,7 @@
           <t>Metal 2</t>
         </is>
       </c>
-      <c r="F11">
+      <c r="F11" t="n">
         <v>8</v>
       </c>
       <c r="G11" t="inlineStr">
@@ -515,7 +916,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2024-03-01</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -533,7 +934,7 @@
           <t>Top Metal</t>
         </is>
       </c>
-      <c r="F12">
+      <c r="F12" t="n">
         <v>6</v>
       </c>
       <c r="G12" t="inlineStr">
@@ -560,12 +961,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2024-03-11</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>LOT-V7-008</t>
+          <t>LOT-V7-005</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -578,7 +979,7 @@
           <t>Active/GOX</t>
         </is>
       </c>
-      <c r="F13">
+      <c r="F13" t="n">
         <v>3</v>
       </c>
       <c r="G13" t="inlineStr">
@@ -605,12 +1006,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2024-03-13</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>LOT-V7-008</t>
+          <t>LOT-V7-005</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -623,7 +1024,7 @@
           <t>Contact/M1</t>
         </is>
       </c>
-      <c r="F14">
+      <c r="F14" t="n">
         <v>3</v>
       </c>
       <c r="G14" t="inlineStr">
@@ -650,7 +1051,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2024-03-20</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -668,7 +1069,7 @@
           <t>Kerf Dicing</t>
         </is>
       </c>
-      <c r="F15">
+      <c r="F15" t="n">
         <v>9</v>
       </c>
       <c r="G15" t="inlineStr">
@@ -695,7 +1096,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2024-03-28</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -713,7 +1114,7 @@
           <t>Metal 1</t>
         </is>
       </c>
-      <c r="F16">
+      <c r="F16" t="n">
         <v>5</v>
       </c>
       <c r="G16" t="inlineStr">
@@ -740,7 +1141,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2024-04-03</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -758,7 +1159,7 @@
           <t>Poly Res</t>
         </is>
       </c>
-      <c r="F17">
+      <c r="F17" t="n">
         <v>12</v>
       </c>
       <c r="G17" t="inlineStr">
@@ -785,7 +1186,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2024-04-21</t>
+          <t>2026-04-19</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -803,7 +1204,7 @@
           <t>Metal 4</t>
         </is>
       </c>
-      <c r="F18">
+      <c r="F18" t="n">
         <v>4</v>
       </c>
       <c r="G18" t="inlineStr">
@@ -830,7 +1231,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2024-04-22</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -848,7 +1249,7 @@
           <t>Polyimide</t>
         </is>
       </c>
-      <c r="F19">
+      <c r="F19" t="n">
         <v>3</v>
       </c>
       <c r="G19" t="inlineStr">
@@ -875,7 +1276,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2024-04-27</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -893,7 +1294,7 @@
           <t>Leadframe</t>
         </is>
       </c>
-      <c r="F20">
+      <c r="F20" t="n">
         <v>2</v>
       </c>
       <c r="G20" t="inlineStr">
@@ -920,7 +1321,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2024-05-03</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -938,7 +1339,7 @@
           <t>Active Salicide</t>
         </is>
       </c>
-      <c r="F21">
+      <c r="F21" t="n">
         <v>5</v>
       </c>
       <c r="G21" t="inlineStr">
@@ -965,7 +1366,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2024-05-09</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -983,7 +1384,7 @@
           <t>Aluminum Pad</t>
         </is>
       </c>
-      <c r="F22">
+      <c r="F22" t="n">
         <v>2</v>
       </c>
       <c r="G22" t="inlineStr">
@@ -1010,7 +1411,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2024-05-15</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1028,7 +1429,7 @@
           <t>QFN Flank</t>
         </is>
       </c>
-      <c r="F23">
+      <c r="F23" t="n">
         <v>4</v>
       </c>
       <c r="G23" t="inlineStr">
@@ -1048,5 +1449,6 @@
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>